--- a/RNR_수입원가_2026_latest.xlsx
+++ b/RNR_수입원가_2026_latest.xlsx
@@ -979,10 +979,11 @@
 (정보기술협정 양허품목)</t>
       </text>
     </comment>
-    <comment ref="S13" authorId="0" shapeId="0">
+    <comment ref="S14" authorId="0" shapeId="0">
       <text>
         <t>ITA(정보기술협정) 관세면제
-HS 8518/8543 디지털시네마장비</t>
+HS 8414.59 — Projector cooling fan
+(WTO 협정세율 0%)</t>
       </text>
     </comment>
     <comment ref="S15" authorId="0" shapeId="0">
